--- a/Customer Rate Tariff Template_Week 32_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 32_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F368B679-C12B-4AC8-8D18-0DEDFB4776B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
